--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>App</t>
   </si>
@@ -72,6 +72,12 @@
   </si>
   <si>
     <t>on</t>
+  </si>
+  <si>
+    <t>HomePage_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70821</t>
   </si>
 </sst>
 </file>
@@ -1050,8 +1056,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
     <col min="4" max="5" width="10.4259259259259" customWidth="1"/>
@@ -1103,14 +1109,37 @@
         <v>13</v>
       </c>
     </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G2" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="C2">
+  <conditionalFormatting sqref="C2:C3">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1 C3:C1048576">
+  <conditionalFormatting sqref="C1 C4:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
   <si>
     <t>App</t>
   </si>
@@ -56,7 +56,7 @@
     <t>.</t>
   </si>
   <si>
-    <t>Account_Overview_[MOB_ANDROID]</t>
+    <t>Placanje_RSD_Nedovoljno_Sredstava[MOB_ANDROID]</t>
   </si>
   <si>
     <t>C70820</t>
@@ -78,6 +78,12 @@
   </si>
   <si>
     <t>C70821</t>
+  </si>
+  <si>
+    <t>Licni_Podaci[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70822</t>
   </si>
 </sst>
 </file>
@@ -1056,8 +1062,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="6"/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
     <col min="4" max="5" width="10.4259259259259" customWidth="1"/>
@@ -1132,14 +1138,37 @@
         <v>13</v>
       </c>
     </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G2" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G4" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="C2:C3">
+  <conditionalFormatting sqref="C2:C4">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1 C4:C1048576">
+  <conditionalFormatting sqref="C1 C5:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="10188"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>App</t>
   </si>
@@ -72,6 +72,12 @@
   </si>
   <si>
     <t>on</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>C70821</t>
   </si>
 </sst>
 </file>
@@ -1050,8 +1056,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
     <col min="4" max="5" width="10.4259259259259" customWidth="1"/>
@@ -1103,14 +1109,34 @@
         <v>13</v>
       </c>
     </row>
+    <row r="3" spans="1:7">
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G2" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="C2">
+  <conditionalFormatting sqref="C2:C3">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1 C3:C1048576">
+  <conditionalFormatting sqref="C1 C4:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="10188"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
   <si>
     <t>App</t>
   </si>
@@ -84,6 +84,18 @@
   </si>
   <si>
     <t>C70822</t>
+  </si>
+  <si>
+    <t>Card_details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70823</t>
+  </si>
+  <si>
+    <t>Offers_overview_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70824</t>
   </si>
 </sst>
 </file>
@@ -1062,8 +1074,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
     <col min="4" max="5" width="10.4259259259259" customWidth="1"/>
@@ -1161,14 +1173,60 @@
         <v>13</v>
       </c>
     </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G4" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G5" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="C2:C4">
+  <conditionalFormatting sqref="C2:C6">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1 C5:C1048576">
+  <conditionalFormatting sqref="C1 C7:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
   <si>
     <t>App</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>C70822</t>
+  </si>
+  <si>
+    <t>Placanje_RSD_Skeniranjem_QR[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70823</t>
   </si>
 </sst>
 </file>
@@ -1062,8 +1068,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
     <col min="4" max="5" width="10.4259259259259" customWidth="1"/>
@@ -1161,14 +1167,37 @@
         <v>13</v>
       </c>
     </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G4" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="C2:C4">
+  <conditionalFormatting sqref="C2:C5">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1 C5:C1048576">
+  <conditionalFormatting sqref="C1 C6:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10188"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="24">
   <si>
     <t>App</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>C70824</t>
+  </si>
+  <si>
+    <t>Placanje_RSD_Skeniranjem_QR[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70825</t>
   </si>
 </sst>
 </file>
@@ -467,7 +473,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -485,6 +491,15 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -612,7 +627,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -624,34 +639,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -736,13 +751,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1074,8 +1090,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="6"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
     <col min="4" max="5" width="10.4259259259259" customWidth="1"/>
@@ -1219,14 +1235,37 @@
         <v>13</v>
       </c>
     </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G5" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G6" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="C2:C6">
+  <conditionalFormatting sqref="C2:C7">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1 C7:C1048576">
+  <conditionalFormatting sqref="C1 C8:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +56,7 @@
     <t>.</t>
   </si>
   <si>
-    <t>Placanje_RSD_Nedovoljno_Sredstava[MOB_ANDROID]</t>
+    <t>Placanje_RSD[MOB_ANDROID]</t>
   </si>
   <si>
     <t>C70820</t>
@@ -473,7 +473,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -488,6 +488,30 @@
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -627,7 +651,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -639,34 +663,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -751,7 +775,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -759,6 +783,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1147,7 +1173,7 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -1170,7 +1196,7 @@
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -1193,7 +1219,7 @@
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1216,7 +1242,7 @@
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1239,13 +1265,13 @@
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -1259,7 +1285,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G6" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G7" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="C2:C7">

--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="10188"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="26">
   <si>
     <t>App</t>
   </si>
@@ -102,6 +102,12 @@
   </si>
   <si>
     <t>C70825</t>
+  </si>
+  <si>
+    <t>Internal_transfer_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70826</t>
   </si>
 </sst>
 </file>
@@ -1090,8 +1096,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
     <col min="4" max="5" width="10.4259259259259" customWidth="1"/>
@@ -1258,14 +1264,37 @@
         <v>13</v>
       </c>
     </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G6" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G7" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C2:C8">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1 C8:C1048576">
+  <conditionalFormatting sqref="C1 C9:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="10188"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="26">
   <si>
     <t>App</t>
   </si>
@@ -102,6 +102,12 @@
   </si>
   <si>
     <t>C70825</t>
+  </si>
+  <si>
+    <t>Internal_transfer_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70826</t>
   </si>
 </sst>
 </file>
@@ -1116,8 +1122,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
     <col min="4" max="5" width="10.4259259259259" customWidth="1"/>
@@ -1284,14 +1290,37 @@
         <v>13</v>
       </c>
     </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G7" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C2:C8">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1 C8:C1048576">
+  <conditionalFormatting sqref="C1 C9:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1314,7 +1314,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G7" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G8" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="C2:C8">

--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10188"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="28">
   <si>
     <t>App</t>
   </si>
@@ -108,6 +108,12 @@
   </si>
   <si>
     <t>C70826</t>
+  </si>
+  <si>
+    <t>Change_Name_Of_Account_RSD[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70827</t>
   </si>
 </sst>
 </file>
@@ -781,7 +787,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -791,6 +797,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1122,8 +1129,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
     <col min="4" max="5" width="10.4259259259259" customWidth="1"/>
@@ -1294,7 +1301,7 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1310,6 +1317,29 @@
         <v>12</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1317,10 +1347,10 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G8" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="C2:C8">
+  <conditionalFormatting sqref="C2:C9">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1 C9:C1048576">
+  <conditionalFormatting sqref="C1 C10:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="30">
   <si>
     <t>App</t>
   </si>
@@ -110,10 +110,16 @@
     <t>C70826</t>
   </si>
   <si>
-    <t>Change_Name_Of_Account_RSD[MOB_ANDROID]</t>
+    <t>Accounts-Domestic_Accounts-Change_name_of_account_[MOB]</t>
   </si>
   <si>
     <t>C70827</t>
+  </si>
+  <si>
+    <t>Accounts-Domestic_Accounts-Change_name_of_account_to_default_[MOB]</t>
+  </si>
+  <si>
+    <t>C70828</t>
   </si>
 </sst>
 </file>
@@ -787,7 +793,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -798,6 +804,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1129,7 +1136,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
@@ -1343,14 +1350,37 @@
         <v>13</v>
       </c>
     </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G8" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="C2:C9">
+  <conditionalFormatting sqref="C2:C10">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1 C10:C1048576">
+  <conditionalFormatting sqref="C1 C11:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="10188"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="32">
   <si>
     <t>App</t>
   </si>
@@ -120,6 +120,12 @@
   </si>
   <si>
     <t>C70828</t>
+  </si>
+  <si>
+    <t>Accounts-Foreign_Accounts-Change_name_of_account_[MOB]</t>
+  </si>
+  <si>
+    <t>Accounts-Foreign_Accounts-Change_name_of_account_to_default_[MOB]</t>
   </si>
 </sst>
 </file>
@@ -793,7 +799,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -803,8 +809,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1136,7 +1140,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
@@ -1308,7 +1312,7 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1331,7 +1335,7 @@
       <c r="A9" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1354,7 +1358,7 @@
       <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1373,15 +1377,64 @@
         <v>13</v>
       </c>
     </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G8" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G10" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="C2:C10">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11:C12">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1 C11:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  <conditionalFormatting sqref="C1 C13:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="33">
   <si>
     <t>App</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>Accounts-Foreign_Accounts-Change_name_of_account_to_default_[MOB]</t>
+  </si>
+  <si>
+    <t>Homepage_Bottom_nav_[MOB_ANDROID]</t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1143,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
@@ -1423,18 +1426,44 @@
         <v>13</v>
       </c>
     </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G10" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G12" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
+  <conditionalFormatting sqref="C13">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C2:C10">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11:C12">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:C12">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1 C13:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  <conditionalFormatting sqref="C1 C14:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="34">
   <si>
     <t>App</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>Homepage_Bottom_nav_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>Homepage_Account_Display_[ANDROID_MOB]</t>
   </si>
 </sst>
 </file>
@@ -1143,7 +1146,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
@@ -1445,7 +1448,30 @@
       <c r="F13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1454,16 +1480,19 @@
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="C13">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C10">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11:C12">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:C12">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1 C14:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  <conditionalFormatting sqref="C1 C15:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
